--- a/data/qa/prospect_to_cash/credit.xlsx
+++ b/data/qa/prospect_to_cash/credit.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0005</t>
+          <t>KB-0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,54 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Credit Review and Credit Hold Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Credit Limit</t>
-        </is>
-      </c>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HELP_FIELD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>field_definition</t>
-        </is>
-      </c>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is Credit Limit?</t>
+          <t>How does SyteLine handle customer credit limits and credit holds?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Credit Limit is the maximum outstanding balance a customer is allowed to carry before new orders are held for credit review.</t>
+          <t>SyteLine distinguishes between customer credit limit, customer-level Credit Hold, and order-level Credit Hold. A customer hold can block shipments without setting every order's checkbox, and automatic over-limit order holds require the Limit Exceeded Credit Hold Reason parameter in Accounts Receivable Parameters.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>credit limit</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>credit ceiling,spending limit</t>
-        </is>
-      </c>
+          <t>credit limit, customer credit hold, order credit hold, Limit Exceeded Credit Hold Reason</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -607,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>credit.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Credit Review and Credit Hold Module &gt; Customer credit, order hold, and parameters</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -631,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -642,7 +640,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -654,7 +652,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA-0016</t>
+          <t>KB-0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -664,50 +662,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Credit Review and Credit Hold Module</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Customer Orders</t>
-        </is>
-      </c>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HELP_GENERIC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>What is a Credit Hold?</t>
+          <t>What determines if an over-limit order is automatically placed on credit hold?</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A Credit Hold is a status placed on a Customer Order when the customer's outstanding balance would exceed their Credit Limit. The order cannot ship until the hold is released.</t>
+          <t>Automatic over-limit order holds require the Limit Exceeded Credit Hold Reason parameter in Accounts Receivable Parameters; if that field is blank, an over-limit order may not be placed on hold by that mechanism. Behavior also depends on Allow Over Credit Limit, customer hierarchy, and site setup.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>credit hold,order hold</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>credit block,order hold</t>
-        </is>
-      </c>
+          <t>Limit Exceeded Credit Hold Reason, over-limit order, credit hold, parameters</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -715,18 +701,16 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>credit.md</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Credit Review and Credit Hold Module &gt; Customer credit, order hold, and parameters</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -739,10 +723,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V3" t="b">
@@ -750,10 +738,598 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I diagnose a credit warning or blocked shipment?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>To diagnose a credit warning or blocked shipment, identify the customer, corporate customer if relevant, order, line, originating site, and shipping site. Check both the customer-level and order-level Credit Hold, including reason and date, and review the customer's limit, posted balance, on-order balance, aging settings, and any order-specific limit using authorized current data. Also, check Accounts Receivable Parameters for the configured over-limit hold reason, inspect Allow Over Credit Limit, and the line's Planned or Ordered status. If EDI or multi-site is involved, inspect its separate validation and originating-site behavior.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>credit warning, blocked shipment, credit hold, diagnose, order</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>credit.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module &gt; Diagnose a credit warning or blocked shipment</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>How should I diagnose a credit warning or blocked shipment in SyteLine?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Investigate the actual hold flags, balances, parameters, and line status before explaining the block. If EDI or multi-site is involved, inspect its separate validation and originating-site behavior. Give the user the observed reason and the responsible AR/credit team, and do not claim the hold is cleared until SyteLine confirms it.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>credit warning, blocked shipment, hold flags, balances, AR/credit team</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>credit.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module &gt; Diagnose a credit warning or blocked shipment</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>How can I place or release a credit hold on a customer or order?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Authorized users can set a customer or order hold manually. The Order Credit Hold Change Utility can place or release holds across selected customer or order ranges and can use aging parameters.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>credit hold, release, Order Credit Hold Change Utility, customer</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>credit.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module &gt; Place or release a hold</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Does releasing an order hold remove all credit blocks for a customer?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Releasing an order hold does not override a separate customer-level hold.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>release, order hold, customer hold, credit block</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>credit.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module &gt; Place or release a hold</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>How does corporate credit affect orders for subordinate customers in a multi-site setup?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Where a subordinate customer uses corporate credit, the parent credit position affects the order. Replicated multi-site balances and originating-site behavior can change the result of a credit check.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>corporate credit, subordinate customer, multi-site credit, originating site</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>credit.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module &gt; Multi-site and subordinate customers</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>How should available credit be determined for corporate and multi-site customers?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Never derive available credit by adding a few visible invoices or orders; use the authorized ERP calculation for that customer and site.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>corporate credit, multi-site credit, available credit, ERP calculation</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>credit.md</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Credit Review and Credit Hold Module &gt; Multi-site and subordinate customers</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -770,36 +1346,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -808,7 +1384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0005</t>
+          <t>KB-0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -818,7 +1394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>explain credit limit</t>
+          <t>What's the difference between customer and order credit holds in SyteLine?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -828,41 +1404,701 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA-0016</t>
+          <t>KB-0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>How are credit limits and holds managed for customers and orders?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>How does the system treat credit holds at customer and order levels?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>explain credit hold</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>When does an order go on credit hold if it exceeds the limit?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What settings control automatic credit holds for over-limit orders?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>How does SyteLine decide to put an over-limit order on hold?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0003</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What steps should I take to find out why a shipment is blocked due to credit?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How can I troubleshoot a credit warning on an order?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0003</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What should I check if a shipment is held for credit reasons?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0004</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What steps do I take to figure out why a shipment is blocked for credit?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0004</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>How do I check the reason for a credit warning in SyteLine?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0004</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What should I do when a shipment is on credit hold?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0005</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How do I manually put a customer or order on credit hold?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0005</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What's the process to release a credit hold?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0005</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Can I use a utility to manage credit holds for multiple orders?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0006</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>If I release an order hold, is the customer still blocked?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0006</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Does removing a hold from an order affect the customer hold?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0006</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Will releasing an order hold clear all holds for that customer?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>How does a parent company's credit impact its subsidiaries' orders?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0007</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>What happens to credit checks for subordinate customers using corporate credit?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0007</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Does the parent credit status influence orders for related sites?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB-0008</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What's the right way to check available credit for multi-site customers?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KB-0008</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Can I just add up invoices to find available credit for corporate accounts?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KB-0008</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>How do I accurately determine available credit for a customer with multiple sites?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
